--- a/templates/data_model_TEMPLATE.xlsx
+++ b/templates/data_model_TEMPLATE.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_GUIDE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_OBJECTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_GENERATORS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUPPLIER" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PART" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PURCHASE_ORDER" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PO_LINE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VW_OTD_SCORECARD" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_RULES" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="_GUIDE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="_OBJECTS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="_GENERATORS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SUPPLIER" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="PART" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PURCHASE_ORDER" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="PO_LINE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VW_OTD_SCORECARD" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="_RULES" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -633,7 +633,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>The five things people get wrong</t>
+          <t>The six things people get wrong</t>
         </is>
       </c>
     </row>
@@ -673,69 +673,76 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>•  On a VIEW sheet, never add a row after the last output column (e.g. a trailing note). The parser has no end marker for the column list -- any row with a non-empty first cell is read as another column and crashes generation with a missing-derivation error.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Authoring checklist (tick before first generation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>☐  Every table has exactly one PK marked (or a composite: several is_pk=Y rows).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>☐  Every FK found — including ones the source system never declared.</t>
+          <t>☐  Every table has exactly one PK marked (or a composite: several is_pk=Y rows).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>☐  Every SIZING fk has cardinality and orphan_pct.</t>
+          <t>☐  Every FK found — including ones the source system never declared.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>☐  Every non-FK column has a generator.</t>
+          <t>☐  Every SIZING fk has cardinality and orphan_pct.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>☐  Every date pair has a temporal_order or bound rule.</t>
+          <t>☐  Every non-FK column has a generator.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>☐  Every computed column has derived/case + a _RULES row.</t>
+          <t>☐  Every date pair has a temporal_order or bound rule.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>☐  Every computed column has derived/case + a _RULES row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>☐  An SME has reviewed distributions (weights, poisson averages, ranges).</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
-    </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Yellow cells in the sample sheets are the ones you normally edit. Row 2 of each sample sheet is a realistic example row.</t>
         </is>
@@ -862,7 +869,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -1152,17 +1158,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Parent's value ± a percentage</t>
+          <t>Parent's value +/- a percentage, then an optional flat multiplier</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>source=PART.unit_cost; jitter_pct=0.15; round=2</t>
+          <t>source=PART.unit_cost; jitter_pct=0.15; round=2 (optional: multiplier=1.2 for a 20% markup)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1033.12 (part costs 1091.73)</t>
+          <t>1033.12 (part costs 1091.73); with multiplier=1.2 -&gt; 1239.74</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1369,7 +1375,7 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>pattern=SUP-####</t>
+          <t>pattern=SUP-#####</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr"/>
@@ -2231,7 +2237,11 @@
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr"/>
-      <c r="K3" s="7" t="inlineStr"/>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
@@ -2385,7 +2395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -2441,7 +2451,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -2541,14 +2550,6 @@
       <c r="C11" s="7" t="inlineStr">
         <is>
           <t>round(on_time_lines / total_lines * 100, 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>NOTE: a VIEW is never generated randomly — the engine computes it from the generated tables, so it always reconciles.</t>
         </is>
       </c>
     </row>
